--- a/erp-server/erp-server-plm/src/main/resources/excel/productCertificateTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productCertificateTemplate.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <r>
       <rPr>
@@ -51,9 +51,6 @@
       </rPr>
       <t>SKU</t>
     </r>
-  </si>
-  <si>
-    <t>品名</t>
   </si>
   <si>
     <r>
@@ -1066,25 +1063,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="16.75" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="17.875" customWidth="1"/>
-    <col min="5" max="5" width="15.75" customWidth="1"/>
-    <col min="6" max="6" width="20.125" customWidth="1"/>
-    <col min="7" max="7" width="14.875" customWidth="1"/>
-    <col min="8" max="8" width="17.125" customWidth="1"/>
-    <col min="9" max="9" width="15.5" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="17.875" customWidth="1"/>
+    <col min="4" max="4" width="15.75" customWidth="1"/>
+    <col min="5" max="5" width="20.125" customWidth="1"/>
+    <col min="6" max="6" width="14.875" customWidth="1"/>
+    <col min="7" max="7" width="17.125" customWidth="1"/>
+    <col min="8" max="8" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -1093,22 +1089,19 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
       <formula1>"产品认证,运输认证,其他认证"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D$1:D$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576">
       <formula1>"CE,RoHS,FCC,FCC ID,TELEC,PSE,IC,KC,其他"</formula1>
     </dataValidation>
   </dataValidations>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productCertificateTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productCertificateTemplate.xlsx
@@ -1097,12 +1097,15 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1 C3:C1048576">
+      <formula1>"CE,RoHS,FCC,FCC ID,TELEC,PSE,IC,KC,其他"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2">
+      <formula1>"CE,RoHS,FCC,FCC ID,TELEC,PSE,IC,KC,其他,运输报告,其他认证"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
       <formula1>"产品认证,运输认证,其他认证"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576">
-      <formula1>"CE,RoHS,FCC,FCC ID,TELEC,PSE,IC,KC,其他"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productCertificateTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productCertificateTemplate.xlsx
@@ -1097,15 +1097,12 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1 C3:C1048576">
-      <formula1>"CE,RoHS,FCC,FCC ID,TELEC,PSE,IC,KC,其他"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2">
-      <formula1>"CE,RoHS,FCC,FCC ID,TELEC,PSE,IC,KC,其他,运输报告,其他认证"</formula1>
-    </dataValidation>
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
       <formula1>"产品认证,运输认证,其他认证"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576">
+      <formula1>"CE,RoHS,FCC,FCC ID,TELEC,PSE,IC,KC,其他,运输报告,其他认证"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productCertificateTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productCertificateTemplate.xlsx
@@ -1102,7 +1102,7 @@
       <formula1>"产品认证,运输认证,其他认证"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576">
-      <formula1>"CE,RoHS,FCC,FCC ID,TELEC,PSE,IC,KC,其他,运输报告,其他认证"</formula1>
+      <formula1>"CE,RoHS,FCC,FCC ID,TELEC,PSE,IC,KC,CCC,质检报告,SRRC,Reach,其他,运输报告,其他认证"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
